--- a/Project Binder/03_Task_Management_and_Logs/Gantt Chart.xlsx
+++ b/Project Binder/03_Task_Management_and_Logs/Gantt Chart.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="119">
   <si>
     <t xml:space="preserve">IN2033 Project</t>
   </si>
@@ -142,9 +142,6 @@
   </si>
   <si>
     <t xml:space="preserve">Haris, Bahja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/2/26</t>
   </si>
   <si>
     <t xml:space="preserve">Test cases</t>
@@ -1669,7 +1666,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:BL98"/>
+  <dimension ref="A1:BL1048576"/>
   <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="30" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.72"/>
@@ -3249,12 +3246,8 @@
       <c r="D20" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="66" t="n">
-        <v>46078</v>
-      </c>
-      <c r="F20" s="66" t="s">
-        <v>37</v>
-      </c>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="44"/>
       <c r="H20" s="45"/>
       <c r="I20" s="52"/>
@@ -3317,10 +3310,10 @@
     <row r="21" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="64" t="s">
         <v>38</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>39</v>
       </c>
       <c r="D21" s="65" t="n">
         <v>1</v>
@@ -3389,10 +3382,10 @@
     <row r="22" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="64" t="s">
         <v>40</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>41</v>
       </c>
       <c r="D22" s="65" t="n">
         <v>1</v>
@@ -3461,7 +3454,7 @@
     <row r="23" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="64" t="s">
         <v>15</v>
@@ -3537,15 +3530,15 @@
     <row r="24" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="B24" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="68"/>
       <c r="D24" s="69"/>
       <c r="E24" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="71" t="s">
         <v>44</v>
-      </c>
-      <c r="F24" s="71" t="s">
-        <v>45</v>
       </c>
       <c r="G24" s="44"/>
       <c r="H24" s="45" t="e">
@@ -3612,7 +3605,7 @@
     <row r="25" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="73" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="74"/>
       <c r="D25" s="75"/>
@@ -3624,7 +3617,7 @@
       </c>
       <c r="G25" s="44"/>
       <c r="H25" s="45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I25" s="52"/>
       <c r="J25" s="52"/>
@@ -3686,10 +3679,10 @@
     <row r="26" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
       <c r="B26" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="78" t="s">
         <v>48</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>49</v>
       </c>
       <c r="D26" s="79" t="n">
         <v>1</v>
@@ -3698,7 +3691,7 @@
       <c r="F26" s="80"/>
       <c r="G26" s="44"/>
       <c r="H26" s="45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I26" s="52"/>
       <c r="J26" s="52"/>
@@ -3760,10 +3753,10 @@
     <row r="27" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1"/>
       <c r="B27" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="78" t="s">
         <v>50</v>
-      </c>
-      <c r="C27" s="78" t="s">
-        <v>51</v>
       </c>
       <c r="D27" s="79" t="n">
         <v>1</v>
@@ -3772,7 +3765,7 @@
       <c r="F27" s="80"/>
       <c r="G27" s="44"/>
       <c r="H27" s="45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I27" s="52"/>
       <c r="J27" s="52"/>
@@ -3834,7 +3827,7 @@
     <row r="28" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
       <c r="B28" s="73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="74"/>
       <c r="D28" s="75"/>
@@ -3846,7 +3839,7 @@
       </c>
       <c r="G28" s="44"/>
       <c r="H28" s="45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I28" s="52"/>
       <c r="J28" s="52"/>
@@ -3908,17 +3901,17 @@
     <row r="29" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" s="79"/>
       <c r="E29" s="80"/>
       <c r="F29" s="80"/>
       <c r="G29" s="44"/>
       <c r="H29" s="45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I29" s="52"/>
       <c r="J29" s="52"/>
@@ -3980,10 +3973,10 @@
     <row r="30" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
       <c r="B30" s="77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" s="79"/>
       <c r="E30" s="80"/>
@@ -4050,10 +4043,10 @@
     <row r="31" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="78" t="s">
         <v>55</v>
-      </c>
-      <c r="C31" s="78" t="s">
-        <v>56</v>
       </c>
       <c r="D31" s="79"/>
       <c r="E31" s="80"/>
@@ -4120,10 +4113,10 @@
     <row r="32" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
       <c r="B32" s="77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="78" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="79"/>
       <c r="E32" s="80"/>
@@ -4190,7 +4183,7 @@
     <row r="33" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1"/>
       <c r="B33" s="73" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" s="74"/>
       <c r="D33" s="75"/>
@@ -4262,10 +4255,10 @@
     <row r="34" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1"/>
       <c r="B34" s="77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C34" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" s="79" t="n">
         <v>1</v>
@@ -4334,10 +4327,10 @@
     <row r="35" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1"/>
       <c r="B35" s="77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35" s="79" t="n">
         <v>1</v>
@@ -4406,10 +4399,10 @@
     <row r="36" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
       <c r="B36" s="77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" s="79" t="n">
         <v>1</v>
@@ -4478,10 +4471,10 @@
     <row r="37" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1"/>
       <c r="B37" s="77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" s="79" t="n">
         <v>1</v>
@@ -4550,10 +4543,10 @@
     <row r="38" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1"/>
       <c r="B38" s="77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" s="79"/>
       <c r="E38" s="80"/>
@@ -4620,10 +4613,10 @@
     <row r="39" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1"/>
       <c r="B39" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C39" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D39" s="79" t="n">
         <v>1</v>
@@ -4692,10 +4685,10 @@
     <row r="40" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1"/>
       <c r="B40" s="77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" s="79" t="n">
         <v>1</v>
@@ -4764,10 +4757,10 @@
     <row r="41" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1"/>
       <c r="B41" s="77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" s="79" t="n">
         <v>1</v>
@@ -4836,10 +4829,10 @@
     <row r="42" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1"/>
       <c r="B42" s="77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C42" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" s="79" t="n">
         <v>1</v>
@@ -4908,10 +4901,10 @@
     <row r="43" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1"/>
       <c r="B43" s="77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D43" s="79" t="n">
         <v>1</v>
@@ -4980,10 +4973,10 @@
     <row r="44" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1"/>
       <c r="B44" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" s="79" t="n">
         <v>1</v>
@@ -5052,10 +5045,10 @@
     <row r="45" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1"/>
       <c r="B45" s="77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" s="78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" s="79" t="n">
         <v>1</v>
@@ -5124,7 +5117,7 @@
     <row r="46" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1"/>
       <c r="B46" s="73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" s="74"/>
       <c r="D46" s="75"/>
@@ -5196,10 +5189,10 @@
     <row r="47" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1"/>
       <c r="B47" s="77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D47" s="79" t="n">
         <v>1</v>
@@ -5268,10 +5261,10 @@
     <row r="48" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1"/>
       <c r="B48" s="77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D48" s="79" t="n">
         <v>1</v>
@@ -5340,10 +5333,10 @@
     <row r="49" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1"/>
       <c r="B49" s="77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D49" s="79"/>
       <c r="E49" s="80"/>
@@ -5410,10 +5403,10 @@
     <row r="50" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1"/>
       <c r="B50" s="77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C50" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" s="79"/>
       <c r="E50" s="80"/>
@@ -5480,10 +5473,10 @@
     <row r="51" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1"/>
       <c r="B51" s="77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D51" s="79" t="n">
         <v>1</v>
@@ -5552,10 +5545,10 @@
     <row r="52" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1"/>
       <c r="B52" s="77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C52" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" s="79" t="n">
         <v>1</v>
@@ -5624,10 +5617,10 @@
     <row r="53" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1"/>
       <c r="B53" s="77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C53" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D53" s="79"/>
       <c r="E53" s="80"/>
@@ -5694,10 +5687,10 @@
     <row r="54" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1"/>
       <c r="B54" s="77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C54" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D54" s="79" t="n">
         <v>1</v>
@@ -5766,10 +5759,10 @@
     <row r="55" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1"/>
       <c r="B55" s="77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C55" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D55" s="79"/>
       <c r="E55" s="80"/>
@@ -5836,10 +5829,10 @@
     <row r="56" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1"/>
       <c r="B56" s="77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" s="79" t="n">
         <v>1</v>
@@ -5908,7 +5901,7 @@
     <row r="57" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1"/>
       <c r="B57" s="73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C57" s="74"/>
       <c r="D57" s="75"/>
@@ -5980,12 +5973,14 @@
     <row r="58" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1"/>
       <c r="B58" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="C58" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="79"/>
+      <c r="D58" s="79" t="n">
+        <v>1</v>
+      </c>
       <c r="E58" s="80"/>
       <c r="F58" s="80"/>
       <c r="G58" s="44"/>
@@ -6050,12 +6045,14 @@
     <row r="59" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1"/>
       <c r="B59" s="77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" s="79"/>
+        <v>82</v>
+      </c>
+      <c r="D59" s="79" t="n">
+        <v>1</v>
+      </c>
       <c r="E59" s="80"/>
       <c r="F59" s="80"/>
       <c r="G59" s="44"/>
@@ -6120,12 +6117,14 @@
     <row r="60" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1"/>
       <c r="B60" s="77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D60" s="79"/>
+        <v>82</v>
+      </c>
+      <c r="D60" s="79" t="n">
+        <v>1</v>
+      </c>
       <c r="E60" s="80"/>
       <c r="F60" s="80"/>
       <c r="G60" s="44"/>
@@ -6190,12 +6189,14 @@
     <row r="61" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1"/>
       <c r="B61" s="77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C61" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="79"/>
+        <v>82</v>
+      </c>
+      <c r="D61" s="79" t="n">
+        <v>1</v>
+      </c>
       <c r="E61" s="80"/>
       <c r="F61" s="80"/>
       <c r="G61" s="44"/>
@@ -6260,12 +6261,14 @@
     <row r="62" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1"/>
       <c r="B62" s="77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D62" s="79"/>
+        <v>82</v>
+      </c>
+      <c r="D62" s="79" t="n">
+        <v>1</v>
+      </c>
       <c r="E62" s="80"/>
       <c r="F62" s="80"/>
       <c r="G62" s="44"/>
@@ -6330,7 +6333,7 @@
     <row r="63" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1"/>
       <c r="B63" s="73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" s="74"/>
       <c r="D63" s="75"/>
@@ -6402,10 +6405,10 @@
     <row r="64" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1"/>
       <c r="B64" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="78" t="s">
         <v>89</v>
-      </c>
-      <c r="C64" s="78" t="s">
-        <v>90</v>
       </c>
       <c r="D64" s="79"/>
       <c r="E64" s="80"/>
@@ -6472,10 +6475,10 @@
     <row r="65" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1"/>
       <c r="B65" s="77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D65" s="79"/>
       <c r="E65" s="80"/>
@@ -6542,10 +6545,10 @@
     <row r="66" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1"/>
       <c r="B66" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" s="78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D66" s="79"/>
       <c r="E66" s="80"/>
@@ -6612,7 +6615,7 @@
     <row r="67" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1"/>
       <c r="B67" s="73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C67" s="74"/>
       <c r="D67" s="75"/>
@@ -6684,10 +6687,10 @@
     <row r="68" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="78" t="s">
         <v>94</v>
-      </c>
-      <c r="C68" s="78" t="s">
-        <v>95</v>
       </c>
       <c r="D68" s="79" t="n">
         <v>1</v>
@@ -6760,10 +6763,10 @@
     <row r="69" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1"/>
       <c r="B69" s="77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="79" t="n">
         <v>1</v>
@@ -6836,10 +6839,10 @@
     <row r="70" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1"/>
       <c r="B70" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" s="78" t="s">
         <v>97</v>
-      </c>
-      <c r="C70" s="78" t="s">
-        <v>98</v>
       </c>
       <c r="D70" s="79" t="n">
         <v>1</v>
@@ -6908,10 +6911,10 @@
     <row r="71" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1"/>
       <c r="B71" s="77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C71" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="79" t="n">
         <v>1</v>
@@ -6980,10 +6983,10 @@
     <row r="72" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1"/>
       <c r="B72" s="77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C72" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D72" s="79"/>
       <c r="E72" s="80"/>
@@ -7050,10 +7053,10 @@
     <row r="73" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1"/>
       <c r="B73" s="77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C73" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D73" s="79"/>
       <c r="E73" s="80" t="n">
@@ -7124,10 +7127,10 @@
     <row r="74" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1"/>
       <c r="B74" s="77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C74" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D74" s="79" t="n">
         <v>1</v>
@@ -7200,10 +7203,10 @@
     <row r="75" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1"/>
       <c r="B75" s="77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C75" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D75" s="79" t="n">
         <v>1</v>
@@ -7276,10 +7279,10 @@
     <row r="76" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1"/>
       <c r="B76" s="77" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C76" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D76" s="79" t="n">
         <v>1</v>
@@ -7352,10 +7355,10 @@
     <row r="77" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1"/>
       <c r="B77" s="77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C77" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D77" s="79" t="n">
         <v>1</v>
@@ -7428,10 +7431,10 @@
     <row r="78" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1"/>
       <c r="B78" s="77" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C78" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="79" t="n">
         <v>1</v>
@@ -7504,10 +7507,10 @@
     <row r="79" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1"/>
       <c r="B79" s="77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D79" s="79" t="n">
         <v>1</v>
@@ -7580,10 +7583,10 @@
     <row r="80" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1"/>
       <c r="B80" s="77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D80" s="79" t="n">
         <v>1</v>
@@ -7652,10 +7655,10 @@
     <row r="81" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1"/>
       <c r="B81" s="77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C81" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D81" s="79" t="n">
         <v>1</v>
@@ -7728,10 +7731,10 @@
     <row r="82" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1"/>
       <c r="B82" s="77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C82" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D82" s="79" t="n">
         <v>1</v>
@@ -7804,10 +7807,10 @@
     <row r="83" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1"/>
       <c r="B83" s="77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C83" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="79" t="n">
         <v>1</v>
@@ -7880,10 +7883,10 @@
     <row r="84" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1"/>
       <c r="B84" s="77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C84" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D84" s="79" t="n">
         <v>1</v>
@@ -7956,7 +7959,7 @@
     <row r="85" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C85" s="74"/>
       <c r="D85" s="75"/>
@@ -8028,10 +8031,10 @@
     <row r="86" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1"/>
       <c r="B86" s="77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C86" s="78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D86" s="79"/>
       <c r="E86" s="80"/>
@@ -8098,7 +8101,7 @@
     <row r="87" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1"/>
       <c r="B87" s="73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C87" s="74"/>
       <c r="D87" s="75"/>
@@ -8170,10 +8173,10 @@
     <row r="88" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1"/>
       <c r="B88" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="C88" s="78" t="s">
         <v>116</v>
-      </c>
-      <c r="C88" s="78" t="s">
-        <v>117</v>
       </c>
       <c r="D88" s="79" t="n">
         <v>1</v>
@@ -8246,7 +8249,7 @@
     <row r="89" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="77" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C89" s="78" t="s">
         <v>15</v>
@@ -8321,418 +8324,158 @@
     </row>
     <row r="90" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="78"/>
-      <c r="D90" s="79"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="83"/>
+      <c r="E90" s="84"/>
+      <c r="F90" s="84"/>
       <c r="G90" s="44"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="52"/>
-      <c r="N90" s="52"/>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
-      <c r="T90" s="52"/>
-      <c r="U90" s="52"/>
-      <c r="V90" s="52"/>
-      <c r="W90" s="52"/>
-      <c r="X90" s="52"/>
-      <c r="Y90" s="52"/>
-      <c r="Z90" s="52"/>
-      <c r="AA90" s="52"/>
-      <c r="AB90" s="52"/>
-      <c r="AC90" s="52"/>
-      <c r="AD90" s="52"/>
-      <c r="AE90" s="52"/>
-      <c r="AF90" s="52"/>
-      <c r="AG90" s="52"/>
-      <c r="AH90" s="52"/>
-      <c r="AI90" s="52"/>
-      <c r="AJ90" s="52"/>
-      <c r="AK90" s="52"/>
-      <c r="AL90" s="52"/>
-      <c r="AM90" s="52"/>
-      <c r="AN90" s="52"/>
-      <c r="AO90" s="52"/>
-      <c r="AP90" s="52"/>
-      <c r="AQ90" s="52"/>
-      <c r="AR90" s="52"/>
-      <c r="AS90" s="52"/>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
-      <c r="AY90" s="52"/>
-      <c r="AZ90" s="52"/>
-      <c r="BA90" s="52"/>
-      <c r="BB90" s="52"/>
-      <c r="BC90" s="52"/>
-      <c r="BD90" s="52"/>
-      <c r="BE90" s="52"/>
-      <c r="BF90" s="52"/>
-      <c r="BG90" s="52"/>
-      <c r="BH90" s="52"/>
-      <c r="BI90" s="52"/>
-      <c r="BJ90" s="52"/>
-      <c r="BK90" s="52"/>
-      <c r="BL90" s="52"/>
-    </row>
-    <row r="91" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="78"/>
-      <c r="D91" s="79"/>
-      <c r="E91" s="80"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="44"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="52"/>
-      <c r="J91" s="52"/>
-      <c r="K91" s="52"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="52"/>
-      <c r="N91" s="52"/>
-      <c r="O91" s="52"/>
-      <c r="P91" s="52"/>
-      <c r="Q91" s="52"/>
-      <c r="R91" s="52"/>
-      <c r="S91" s="52"/>
-      <c r="T91" s="52"/>
-      <c r="U91" s="52"/>
-      <c r="V91" s="52"/>
-      <c r="W91" s="52"/>
-      <c r="X91" s="52"/>
-      <c r="Y91" s="52"/>
-      <c r="Z91" s="52"/>
-      <c r="AA91" s="52"/>
-      <c r="AB91" s="52"/>
-      <c r="AC91" s="52"/>
-      <c r="AD91" s="52"/>
-      <c r="AE91" s="52"/>
-      <c r="AF91" s="52"/>
-      <c r="AG91" s="52"/>
-      <c r="AH91" s="52"/>
-      <c r="AI91" s="52"/>
-      <c r="AJ91" s="52"/>
-      <c r="AK91" s="52"/>
-      <c r="AL91" s="52"/>
-      <c r="AM91" s="52"/>
-      <c r="AN91" s="52"/>
-      <c r="AO91" s="52"/>
-      <c r="AP91" s="52"/>
-      <c r="AQ91" s="52"/>
-      <c r="AR91" s="52"/>
-      <c r="AS91" s="52"/>
-      <c r="AT91" s="52"/>
-      <c r="AU91" s="52"/>
-      <c r="AV91" s="52"/>
-      <c r="AW91" s="52"/>
-      <c r="AX91" s="52"/>
-      <c r="AY91" s="52"/>
-      <c r="AZ91" s="52"/>
-      <c r="BA91" s="52"/>
-      <c r="BB91" s="52"/>
-      <c r="BC91" s="52"/>
-      <c r="BD91" s="52"/>
-      <c r="BE91" s="52"/>
-      <c r="BF91" s="52"/>
-      <c r="BG91" s="52"/>
-      <c r="BH91" s="52"/>
-      <c r="BI91" s="52"/>
-      <c r="BJ91" s="52"/>
-      <c r="BK91" s="52"/>
-      <c r="BL91" s="52"/>
-    </row>
-    <row r="92" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="78"/>
-      <c r="D92" s="79"/>
-      <c r="E92" s="80"/>
-      <c r="F92" s="80"/>
-      <c r="G92" s="44"/>
-      <c r="H92" s="45"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
-      <c r="L92" s="52"/>
-      <c r="M92" s="52"/>
-      <c r="N92" s="52"/>
-      <c r="O92" s="52"/>
-      <c r="P92" s="52"/>
-      <c r="Q92" s="52"/>
-      <c r="R92" s="52"/>
-      <c r="S92" s="52"/>
-      <c r="T92" s="52"/>
-      <c r="U92" s="52"/>
-      <c r="V92" s="52"/>
-      <c r="W92" s="52"/>
-      <c r="X92" s="52"/>
-      <c r="Y92" s="52"/>
-      <c r="Z92" s="52"/>
-      <c r="AA92" s="52"/>
-      <c r="AB92" s="52"/>
-      <c r="AC92" s="52"/>
-      <c r="AD92" s="52"/>
-      <c r="AE92" s="52"/>
-      <c r="AF92" s="52"/>
-      <c r="AG92" s="52"/>
-      <c r="AH92" s="52"/>
-      <c r="AI92" s="52"/>
-      <c r="AJ92" s="52"/>
-      <c r="AK92" s="52"/>
-      <c r="AL92" s="52"/>
-      <c r="AM92" s="52"/>
-      <c r="AN92" s="52"/>
-      <c r="AO92" s="52"/>
-      <c r="AP92" s="52"/>
-      <c r="AQ92" s="52"/>
-      <c r="AR92" s="52"/>
-      <c r="AS92" s="52"/>
-      <c r="AT92" s="52"/>
-      <c r="AU92" s="52"/>
-      <c r="AV92" s="52"/>
-      <c r="AW92" s="52"/>
-      <c r="AX92" s="52"/>
-      <c r="AY92" s="52"/>
-      <c r="AZ92" s="52"/>
-      <c r="BA92" s="52"/>
-      <c r="BB92" s="52"/>
-      <c r="BC92" s="52"/>
-      <c r="BD92" s="52"/>
-      <c r="BE92" s="52"/>
-      <c r="BF92" s="52"/>
-      <c r="BG92" s="52"/>
-      <c r="BH92" s="52"/>
-      <c r="BI92" s="52"/>
-      <c r="BJ92" s="52"/>
-      <c r="BK92" s="52"/>
-      <c r="BL92" s="52"/>
-    </row>
-    <row r="93" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1"/>
-      <c r="B93" s="77"/>
-      <c r="C93" s="78"/>
-      <c r="D93" s="79"/>
-      <c r="E93" s="80"/>
-      <c r="F93" s="80"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="45"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="52"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="52"/>
-      <c r="O93" s="52"/>
-      <c r="P93" s="52"/>
-      <c r="Q93" s="52"/>
-      <c r="R93" s="52"/>
-      <c r="S93" s="52"/>
-      <c r="T93" s="52"/>
-      <c r="U93" s="52"/>
-      <c r="V93" s="52"/>
-      <c r="W93" s="52"/>
-      <c r="X93" s="52"/>
-      <c r="Y93" s="52"/>
-      <c r="Z93" s="52"/>
-      <c r="AA93" s="52"/>
-      <c r="AB93" s="52"/>
-      <c r="AC93" s="52"/>
-      <c r="AD93" s="52"/>
-      <c r="AE93" s="52"/>
-      <c r="AF93" s="52"/>
-      <c r="AG93" s="52"/>
-      <c r="AH93" s="52"/>
-      <c r="AI93" s="52"/>
-      <c r="AJ93" s="52"/>
-      <c r="AK93" s="52"/>
-      <c r="AL93" s="52"/>
-      <c r="AM93" s="52"/>
-      <c r="AN93" s="52"/>
-      <c r="AO93" s="52"/>
-      <c r="AP93" s="52"/>
-      <c r="AQ93" s="52"/>
-      <c r="AR93" s="52"/>
-      <c r="AS93" s="52"/>
-      <c r="AT93" s="52"/>
-      <c r="AU93" s="52"/>
-      <c r="AV93" s="52"/>
-      <c r="AW93" s="52"/>
-      <c r="AX93" s="52"/>
-      <c r="AY93" s="52"/>
-      <c r="AZ93" s="52"/>
-      <c r="BA93" s="52"/>
-      <c r="BB93" s="52"/>
-      <c r="BC93" s="52"/>
-      <c r="BD93" s="52"/>
-      <c r="BE93" s="52"/>
-      <c r="BF93" s="52"/>
-      <c r="BG93" s="52"/>
-      <c r="BH93" s="52"/>
-      <c r="BI93" s="52"/>
-      <c r="BJ93" s="52"/>
-      <c r="BK93" s="52"/>
-      <c r="BL93" s="52"/>
-    </row>
-    <row r="94" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1"/>
-      <c r="B94" s="81"/>
-      <c r="C94" s="82"/>
-      <c r="D94" s="83"/>
-      <c r="E94" s="84"/>
-      <c r="F94" s="84"/>
-      <c r="G94" s="44"/>
-      <c r="H94" s="45" t="str">
+      <c r="H90" s="45" t="str">
         <f aca="false">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I94" s="46"/>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-      <c r="L94" s="46"/>
-      <c r="M94" s="46"/>
-      <c r="N94" s="46"/>
-      <c r="O94" s="46"/>
-      <c r="P94" s="46"/>
-      <c r="Q94" s="46"/>
-      <c r="R94" s="46"/>
-      <c r="S94" s="46"/>
-      <c r="T94" s="46"/>
-      <c r="U94" s="46"/>
-      <c r="V94" s="46"/>
-      <c r="W94" s="46"/>
-      <c r="X94" s="46"/>
-      <c r="Y94" s="46"/>
-      <c r="Z94" s="46"/>
-      <c r="AA94" s="46"/>
-      <c r="AB94" s="46"/>
-      <c r="AC94" s="46"/>
-      <c r="AD94" s="46"/>
-      <c r="AE94" s="46"/>
-      <c r="AF94" s="46"/>
-      <c r="AG94" s="46"/>
-      <c r="AH94" s="46"/>
-      <c r="AI94" s="46"/>
-      <c r="AJ94" s="46"/>
-      <c r="AK94" s="46"/>
-      <c r="AL94" s="46"/>
-      <c r="AM94" s="46"/>
-      <c r="AN94" s="46"/>
-      <c r="AO94" s="46"/>
-      <c r="AP94" s="46"/>
-      <c r="AQ94" s="46"/>
-      <c r="AR94" s="46"/>
-      <c r="AS94" s="46"/>
-      <c r="AT94" s="46"/>
-      <c r="AU94" s="46"/>
-      <c r="AV94" s="46"/>
-      <c r="AW94" s="46"/>
-      <c r="AX94" s="46"/>
-      <c r="AY94" s="46"/>
-      <c r="AZ94" s="46"/>
-      <c r="BA94" s="46"/>
-      <c r="BB94" s="46"/>
-      <c r="BC94" s="46"/>
-      <c r="BD94" s="46"/>
-      <c r="BE94" s="46"/>
-      <c r="BF94" s="46"/>
-      <c r="BG94" s="46"/>
-      <c r="BH94" s="46"/>
-      <c r="BI94" s="46"/>
-      <c r="BJ94" s="46"/>
-      <c r="BK94" s="46"/>
-      <c r="BL94" s="46"/>
-    </row>
-    <row r="95" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4"/>
-      <c r="B95" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="C95" s="86"/>
-      <c r="D95" s="87"/>
-      <c r="E95" s="88"/>
-      <c r="F95" s="89"/>
-      <c r="G95" s="44"/>
-      <c r="H95" s="90" t="str">
+      <c r="I90" s="46"/>
+      <c r="J90" s="46"/>
+      <c r="K90" s="46"/>
+      <c r="L90" s="46"/>
+      <c r="M90" s="46"/>
+      <c r="N90" s="46"/>
+      <c r="O90" s="46"/>
+      <c r="P90" s="46"/>
+      <c r="Q90" s="46"/>
+      <c r="R90" s="46"/>
+      <c r="S90" s="46"/>
+      <c r="T90" s="46"/>
+      <c r="U90" s="46"/>
+      <c r="V90" s="46"/>
+      <c r="W90" s="46"/>
+      <c r="X90" s="46"/>
+      <c r="Y90" s="46"/>
+      <c r="Z90" s="46"/>
+      <c r="AA90" s="46"/>
+      <c r="AB90" s="46"/>
+      <c r="AC90" s="46"/>
+      <c r="AD90" s="46"/>
+      <c r="AE90" s="46"/>
+      <c r="AF90" s="46"/>
+      <c r="AG90" s="46"/>
+      <c r="AH90" s="46"/>
+      <c r="AI90" s="46"/>
+      <c r="AJ90" s="46"/>
+      <c r="AK90" s="46"/>
+      <c r="AL90" s="46"/>
+      <c r="AM90" s="46"/>
+      <c r="AN90" s="46"/>
+      <c r="AO90" s="46"/>
+      <c r="AP90" s="46"/>
+      <c r="AQ90" s="46"/>
+      <c r="AR90" s="46"/>
+      <c r="AS90" s="46"/>
+      <c r="AT90" s="46"/>
+      <c r="AU90" s="46"/>
+      <c r="AV90" s="46"/>
+      <c r="AW90" s="46"/>
+      <c r="AX90" s="46"/>
+      <c r="AY90" s="46"/>
+      <c r="AZ90" s="46"/>
+      <c r="BA90" s="46"/>
+      <c r="BB90" s="46"/>
+      <c r="BC90" s="46"/>
+      <c r="BD90" s="46"/>
+      <c r="BE90" s="46"/>
+      <c r="BF90" s="46"/>
+      <c r="BG90" s="46"/>
+      <c r="BH90" s="46"/>
+      <c r="BI90" s="46"/>
+      <c r="BJ90" s="46"/>
+      <c r="BK90" s="46"/>
+      <c r="BL90" s="46"/>
+    </row>
+    <row r="91" s="47" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4"/>
+      <c r="B91" s="85" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" s="86"/>
+      <c r="D91" s="87"/>
+      <c r="E91" s="88"/>
+      <c r="F91" s="89"/>
+      <c r="G91" s="44"/>
+      <c r="H91" s="90" t="str">
         <f aca="false">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I95" s="91"/>
-      <c r="J95" s="91"/>
-      <c r="K95" s="91"/>
-      <c r="L95" s="91"/>
-      <c r="M95" s="91"/>
-      <c r="N95" s="91"/>
-      <c r="O95" s="91"/>
-      <c r="P95" s="91"/>
-      <c r="Q95" s="91"/>
-      <c r="R95" s="91"/>
-      <c r="S95" s="91"/>
-      <c r="T95" s="91"/>
-      <c r="U95" s="91"/>
-      <c r="V95" s="91"/>
-      <c r="W95" s="91"/>
-      <c r="X95" s="91"/>
-      <c r="Y95" s="91"/>
-      <c r="Z95" s="91"/>
-      <c r="AA95" s="91"/>
-      <c r="AB95" s="91"/>
-      <c r="AC95" s="91"/>
-      <c r="AD95" s="91"/>
-      <c r="AE95" s="91"/>
-      <c r="AF95" s="91"/>
-      <c r="AG95" s="91"/>
-      <c r="AH95" s="91"/>
-      <c r="AI95" s="91"/>
-      <c r="AJ95" s="91"/>
-      <c r="AK95" s="91"/>
-      <c r="AL95" s="91"/>
-      <c r="AM95" s="91"/>
-      <c r="AN95" s="91"/>
-      <c r="AO95" s="91"/>
-      <c r="AP95" s="91"/>
-      <c r="AQ95" s="91"/>
-      <c r="AR95" s="91"/>
-      <c r="AS95" s="91"/>
-      <c r="AT95" s="91"/>
-      <c r="AU95" s="91"/>
-      <c r="AV95" s="91"/>
-      <c r="AW95" s="91"/>
-      <c r="AX95" s="91"/>
-      <c r="AY95" s="91"/>
-      <c r="AZ95" s="91"/>
-      <c r="BA95" s="91"/>
-      <c r="BB95" s="91"/>
-      <c r="BC95" s="91"/>
-      <c r="BD95" s="91"/>
-      <c r="BE95" s="91"/>
-      <c r="BF95" s="91"/>
-      <c r="BG95" s="91"/>
-      <c r="BH95" s="91"/>
-      <c r="BI95" s="91"/>
-      <c r="BJ95" s="91"/>
-      <c r="BK95" s="91"/>
-      <c r="BL95" s="91"/>
-    </row>
-    <row r="96" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G96" s="92"/>
-    </row>
-    <row r="97" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C97" s="93"/>
-      <c r="F97" s="94"/>
-    </row>
-    <row r="98" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C98" s="95"/>
-    </row>
+      <c r="I91" s="91"/>
+      <c r="J91" s="91"/>
+      <c r="K91" s="91"/>
+      <c r="L91" s="91"/>
+      <c r="M91" s="91"/>
+      <c r="N91" s="91"/>
+      <c r="O91" s="91"/>
+      <c r="P91" s="91"/>
+      <c r="Q91" s="91"/>
+      <c r="R91" s="91"/>
+      <c r="S91" s="91"/>
+      <c r="T91" s="91"/>
+      <c r="U91" s="91"/>
+      <c r="V91" s="91"/>
+      <c r="W91" s="91"/>
+      <c r="X91" s="91"/>
+      <c r="Y91" s="91"/>
+      <c r="Z91" s="91"/>
+      <c r="AA91" s="91"/>
+      <c r="AB91" s="91"/>
+      <c r="AC91" s="91"/>
+      <c r="AD91" s="91"/>
+      <c r="AE91" s="91"/>
+      <c r="AF91" s="91"/>
+      <c r="AG91" s="91"/>
+      <c r="AH91" s="91"/>
+      <c r="AI91" s="91"/>
+      <c r="AJ91" s="91"/>
+      <c r="AK91" s="91"/>
+      <c r="AL91" s="91"/>
+      <c r="AM91" s="91"/>
+      <c r="AN91" s="91"/>
+      <c r="AO91" s="91"/>
+      <c r="AP91" s="91"/>
+      <c r="AQ91" s="91"/>
+      <c r="AR91" s="91"/>
+      <c r="AS91" s="91"/>
+      <c r="AT91" s="91"/>
+      <c r="AU91" s="91"/>
+      <c r="AV91" s="91"/>
+      <c r="AW91" s="91"/>
+      <c r="AX91" s="91"/>
+      <c r="AY91" s="91"/>
+      <c r="AZ91" s="91"/>
+      <c r="BA91" s="91"/>
+      <c r="BB91" s="91"/>
+      <c r="BC91" s="91"/>
+      <c r="BD91" s="91"/>
+      <c r="BE91" s="91"/>
+      <c r="BF91" s="91"/>
+      <c r="BG91" s="91"/>
+      <c r="BH91" s="91"/>
+      <c r="BI91" s="91"/>
+      <c r="BJ91" s="91"/>
+      <c r="BK91" s="91"/>
+      <c r="BL91" s="91"/>
+    </row>
+    <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G92" s="92"/>
+    </row>
+    <row r="93" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C93" s="93"/>
+      <c r="F93" s="94"/>
+    </row>
+    <row r="94" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C94" s="95"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="I1:O1"/>
@@ -8754,12 +8497,12 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:BL93">
+  <conditionalFormatting sqref="I4:BL89">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I25:BL93">
+  <conditionalFormatting sqref="I25:BL89">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -8783,7 +8526,7 @@
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D24:D95 D7:D15">
+  <conditionalFormatting sqref="D24:D91 D7:D15">
     <cfRule type="dataBar" priority="9">
       <dataBar showValue="1" minLength="10" maxLength="90">
         <cfvo type="num" val="0"/>
@@ -8792,7 +8535,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7B549E5A-D8C7-44B7-9622-79FB943F331E}</x14:id>
+          <x14:id>{B7FFCD48-D64D-441E-AA47-21D1699AACF9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8806,7 +8549,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80E6867B-BB66-4B14-B4AF-F874F38A9010}</x14:id>
+          <x14:id>{451039AA-24F5-42AF-B4B0-106FAD7A6180}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8856,7 +8599,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. &#10;Insert new rows ABOVE this one to continue building out your Project Schedule." showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A95" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. &#10;Insert new rows ABOVE this one to continue building out your Project Schedule." showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A91" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8874,7 +8617,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7B549E5A-D8C7-44B7-9622-79FB943F331E}">
+          <x14:cfRule type="dataBar" id="{B7FFCD48-D64D-441E-AA47-21D1699AACF9}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="false">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8886,10 +8629,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D24:D95 D7:D15</xm:sqref>
+          <xm:sqref>D24:D91 D7:D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{80E6867B-BB66-4B14-B4AF-F874F38A9010}">
+          <x14:cfRule type="dataBar" id="{451039AA-24F5-42AF-B4B0-106FAD7A6180}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="false">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
